--- a/data/industry/CFM/eMCP.xlsx
+++ b/data/industry/CFM/eMCP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33386BED-CBED-4733-AAC3-93A30D8997F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004E4412-B187-420D-A4E2-CFAA56EF9B22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -442,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1083,7 +1083,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -1096,6 +1096,121 @@
       </c>
       <c r="G28" s="10">
         <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>63</v>
+      </c>
+      <c r="F29" s="10">
+        <v>65.7</v>
+      </c>
+      <c r="G29" s="10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>63</v>
+      </c>
+      <c r="F30" s="10">
+        <v>65.7</v>
+      </c>
+      <c r="G30" s="10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>63</v>
+      </c>
+      <c r="F31" s="10">
+        <v>65.7</v>
+      </c>
+      <c r="G31" s="10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>80</v>
+      </c>
+      <c r="F32" s="10">
+        <v>82.7</v>
+      </c>
+      <c r="G32" s="10">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>82</v>
+      </c>
+      <c r="F33" s="10">
+        <v>84.7</v>
+      </c>
+      <c r="G33" s="10">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6D90D4-0805-4F1F-B873-D654865F68EF}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1747,7 +1862,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -1760,6 +1875,121 @@
       </c>
       <c r="G28" s="10">
         <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="F29" s="10">
+        <v>74.5</v>
+      </c>
+      <c r="G29" s="10">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="F30" s="10">
+        <v>74.5</v>
+      </c>
+      <c r="G30" s="10">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="F31" s="10">
+        <v>74.5</v>
+      </c>
+      <c r="G31" s="10">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="F32" s="10">
+        <v>90.5</v>
+      </c>
+      <c r="G32" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="F33" s="10">
+        <v>90.5</v>
+      </c>
+      <c r="G33" s="10">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1770,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F328918B-C38E-4C53-9F1E-0761925FE522}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2412,7 +2642,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -2425,6 +2655,121 @@
       </c>
       <c r="G28" s="10">
         <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>88.5</v>
+      </c>
+      <c r="F29" s="10">
+        <v>91</v>
+      </c>
+      <c r="G29" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>88.5</v>
+      </c>
+      <c r="F30" s="10">
+        <v>91</v>
+      </c>
+      <c r="G30" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>88.5</v>
+      </c>
+      <c r="F31" s="10">
+        <v>91</v>
+      </c>
+      <c r="G31" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>101.5</v>
+      </c>
+      <c r="F32" s="10">
+        <v>104</v>
+      </c>
+      <c r="G32" s="10">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>101.5</v>
+      </c>
+      <c r="F33" s="10">
+        <v>104</v>
+      </c>
+      <c r="G33" s="10">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/eMCP.xlsx
+++ b/data/industry/CFM/eMCP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F644DE3-3E62-42E0-B185-0C9C2BA8915B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433E6C54-E153-48F3-978B-21541CAAC8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -69,23 +69,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -98,7 +98,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -129,38 +129,38 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -442,19 +442,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -500,7 +500,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -523,7 +523,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -546,7 +546,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -569,7 +569,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -592,7 +592,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -615,7 +615,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -638,7 +638,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -661,7 +661,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -684,7 +684,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -730,7 +730,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -753,7 +753,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -776,7 +776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -799,7 +799,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -822,7 +822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -845,7 +845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -868,7 +868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -891,7 +891,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -914,7 +914,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -937,7 +937,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -960,7 +960,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -983,7 +983,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -1349,6 +1349,144 @@
       </c>
       <c r="G39" s="10">
         <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>82</v>
+      </c>
+      <c r="F40" s="10">
+        <v>84.7</v>
+      </c>
+      <c r="G40" s="10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>78</v>
+      </c>
+      <c r="F41" s="10">
+        <v>80.7</v>
+      </c>
+      <c r="G41" s="10">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>78</v>
+      </c>
+      <c r="F42" s="10">
+        <v>80.7</v>
+      </c>
+      <c r="G42" s="10">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>77</v>
+      </c>
+      <c r="F43" s="10">
+        <v>79.7</v>
+      </c>
+      <c r="G43" s="10">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>77</v>
+      </c>
+      <c r="F44" s="10">
+        <v>79.7</v>
+      </c>
+      <c r="G44" s="10">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>77</v>
+      </c>
+      <c r="F45" s="10">
+        <v>79.7</v>
+      </c>
+      <c r="G45" s="10">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1359,19 +1497,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6D90D4-0805-4F1F-B873-D654865F68EF}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1394,7 +1532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -1417,7 +1555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -1440,7 +1578,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -1463,7 +1601,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -1486,7 +1624,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -1509,7 +1647,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -1532,7 +1670,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -1555,7 +1693,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -1578,7 +1716,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -1601,7 +1739,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -1624,7 +1762,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -1647,7 +1785,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -1670,7 +1808,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -1693,7 +1831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -1716,7 +1854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -1739,7 +1877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -1762,7 +1900,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -1785,7 +1923,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -1808,7 +1946,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -1831,7 +1969,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -1854,7 +1992,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -1877,7 +2015,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -1900,7 +2038,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1923,7 +2061,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1946,7 +2084,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1969,7 +2107,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -1992,7 +2130,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -2015,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2038,7 +2176,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2061,7 +2199,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -2084,7 +2222,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -2107,7 +2245,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -2130,7 +2268,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -2153,7 +2291,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -2176,7 +2314,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -2199,7 +2337,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -2222,7 +2360,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -2245,7 +2383,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -2266,6 +2404,144 @@
       </c>
       <c r="G39" s="10">
         <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333332898</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F40" s="10">
+        <v>92.5</v>
+      </c>
+      <c r="G40" s="10">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333332699</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>85.5</v>
+      </c>
+      <c r="F41" s="10">
+        <v>88.5</v>
+      </c>
+      <c r="G41" s="10">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333332599</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>85.5</v>
+      </c>
+      <c r="F42" s="10">
+        <v>88.5</v>
+      </c>
+      <c r="G42" s="10">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333332499</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>84.5</v>
+      </c>
+      <c r="F43" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G43" s="10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333332399</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>84.5</v>
+      </c>
+      <c r="F44" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G44" s="10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333332299</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>84.5</v>
+      </c>
+      <c r="F45" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G45" s="10">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2277,20 +2553,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F328918B-C38E-4C53-9F1E-0761925FE522}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="10"/>
-    <col min="6" max="6" width="10.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2313,7 +2589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -2336,7 +2612,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -2359,7 +2635,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -2382,7 +2658,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -2405,7 +2681,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -2428,7 +2704,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -2451,7 +2727,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -2474,7 +2750,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -2497,7 +2773,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -2520,7 +2796,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -2543,7 +2819,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -2566,7 +2842,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -2589,7 +2865,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -2612,7 +2888,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -2635,7 +2911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -2658,7 +2934,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -2681,7 +2957,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -2704,7 +2980,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -2727,7 +3003,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -2750,7 +3026,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -2773,7 +3049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -2796,7 +3072,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -2819,7 +3095,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -2842,7 +3118,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -2865,7 +3141,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -2888,7 +3164,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2911,7 +3187,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -2934,7 +3210,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2957,7 +3233,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2980,7 +3256,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -3003,7 +3279,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -3026,7 +3302,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -3049,7 +3325,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -3072,7 +3348,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -3095,7 +3371,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -3118,7 +3394,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -3141,7 +3417,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -3164,7 +3440,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -3185,6 +3461,144 @@
       </c>
       <c r="G39" s="10">
         <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333332898</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>110.5</v>
+      </c>
+      <c r="F40" s="10">
+        <v>113</v>
+      </c>
+      <c r="G40" s="10">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333332699</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>107.5</v>
+      </c>
+      <c r="F41" s="10">
+        <v>110</v>
+      </c>
+      <c r="G41" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333332599</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>107.5</v>
+      </c>
+      <c r="F42" s="10">
+        <v>110</v>
+      </c>
+      <c r="G42" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333332499</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>105.5</v>
+      </c>
+      <c r="F43" s="10">
+        <v>108</v>
+      </c>
+      <c r="G43" s="10">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333332399</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>105.5</v>
+      </c>
+      <c r="F44" s="10">
+        <v>108</v>
+      </c>
+      <c r="G44" s="10">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333332299</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>105.5</v>
+      </c>
+      <c r="F45" s="10">
+        <v>108</v>
+      </c>
+      <c r="G45" s="10">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
